--- a/docs/verification/files/rocscience/joints/rj005.xlsx
+++ b/docs/verification/files/rocscience/joints/rj005.xlsx
@@ -15258,17 +15258,9 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>560.0</v>
-      </c>
-      <c r="B3" s="3">
-        <v>140.0</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
       <c r="E3" t="s">
         <v>221</v>
       </c>
@@ -15277,17 +15269,9 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>377.7855871052</v>
-      </c>
-      <c r="B4" s="3">
-        <v>400.0</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
       <c r="E4" t="s">
         <v>223</v>
       </c>

--- a/docs/verification/files/rocscience/joints/rj005.xlsx
+++ b/docs/verification/files/rocscience/joints/rj005.xlsx
@@ -3374,7 +3374,9 @@
       <c r="G16" t="s">
         <v>34</v>
       </c>
-      <c r="D16"/>
+      <c r="D16">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>

--- a/docs/verification/files/rocscience/joints/rj005.xlsx
+++ b/docs/verification/files/rocscience/joints/rj005.xlsx
@@ -4939,9 +4939,7 @@
       <c r="F3" s="3">
         <v>0.0</v>
       </c>
-      <c r="G3" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3">
         <v>40.0</v>
       </c>
@@ -4978,9 +4976,7 @@
       <c r="F4" s="3">
         <v>0.0</v>
       </c>
-      <c r="G4" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3">
         <v>40.0</v>
       </c>
@@ -5017,9 +5013,7 @@
       <c r="F5" s="3">
         <v>0.0</v>
       </c>
-      <c r="G5" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G5" s="3"/>
       <c r="H5" s="3">
         <v>40.0</v>
       </c>
@@ -5056,9 +5050,7 @@
       <c r="F6" s="3">
         <v>0.0</v>
       </c>
-      <c r="G6" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="3">
         <v>40.0</v>
       </c>
@@ -5095,9 +5087,7 @@
       <c r="F7" s="3">
         <v>0.0</v>
       </c>
-      <c r="G7" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3">
         <v>40.0</v>
       </c>
@@ -5134,9 +5124,7 @@
       <c r="F8" s="3">
         <v>0.0</v>
       </c>
-      <c r="G8" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G8" s="3"/>
       <c r="H8" s="3">
         <v>40.0</v>
       </c>
@@ -5173,9 +5161,7 @@
       <c r="F9" s="3">
         <v>0.0</v>
       </c>
-      <c r="G9" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G9" s="3"/>
       <c r="H9" s="3">
         <v>40.0</v>
       </c>
@@ -5212,9 +5198,7 @@
       <c r="F10" s="3">
         <v>0.0</v>
       </c>
-      <c r="G10" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G10" s="3"/>
       <c r="H10" s="3">
         <v>40.0</v>
       </c>
@@ -5251,9 +5235,7 @@
       <c r="F11" s="3">
         <v>0.0</v>
       </c>
-      <c r="G11" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G11" s="3"/>
       <c r="H11" s="3">
         <v>40.0</v>
       </c>
@@ -5290,9 +5272,7 @@
       <c r="F12" s="3">
         <v>0.0</v>
       </c>
-      <c r="G12" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G12" s="3"/>
       <c r="H12" s="3">
         <v>40.0</v>
       </c>
@@ -5329,9 +5309,7 @@
       <c r="F13" s="3">
         <v>0.0</v>
       </c>
-      <c r="G13" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3">
         <v>40.0</v>
       </c>
@@ -5368,9 +5346,7 @@
       <c r="F14" s="3">
         <v>0.0</v>
       </c>
-      <c r="G14" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G14" s="3"/>
       <c r="H14" s="3">
         <v>40.0</v>
       </c>
@@ -5407,9 +5383,7 @@
       <c r="F15" s="3">
         <v>0.0</v>
       </c>
-      <c r="G15" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G15" s="3"/>
       <c r="H15" s="3">
         <v>40.0</v>
       </c>
@@ -5446,9 +5420,7 @@
       <c r="F16" s="3">
         <v>0.0</v>
       </c>
-      <c r="G16" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="3">
         <v>40.0</v>
       </c>
@@ -5485,9 +5457,7 @@
       <c r="F17" s="3">
         <v>0.0</v>
       </c>
-      <c r="G17" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="3">
         <v>40.0</v>
       </c>
@@ -5524,9 +5494,7 @@
       <c r="F18" s="3">
         <v>0.0</v>
       </c>
-      <c r="G18" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="3">
         <v>40.0</v>
       </c>
@@ -5563,9 +5531,7 @@
       <c r="F19" s="3">
         <v>0.0</v>
       </c>
-      <c r="G19" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G19" s="3"/>
       <c r="H19" s="3">
         <v>40.0</v>
       </c>
@@ -5602,9 +5568,7 @@
       <c r="F20" s="3">
         <v>0.0</v>
       </c>
-      <c r="G20" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="3">
         <v>40.0</v>
       </c>
@@ -5641,9 +5605,7 @@
       <c r="F21" s="3">
         <v>0.0</v>
       </c>
-      <c r="G21" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="3">
         <v>40.0</v>
       </c>
@@ -5680,9 +5642,7 @@
       <c r="F22" s="3">
         <v>0.0</v>
       </c>
-      <c r="G22" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G22" s="3"/>
       <c r="H22" s="3">
         <v>40.0</v>
       </c>
@@ -5719,9 +5679,7 @@
       <c r="F23" s="3">
         <v>0.0</v>
       </c>
-      <c r="G23" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="3">
         <v>40.0</v>
       </c>
@@ -5758,9 +5716,7 @@
       <c r="F24" s="3">
         <v>0.0</v>
       </c>
-      <c r="G24" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="3">
         <v>40.0</v>
       </c>
@@ -5797,9 +5753,7 @@
       <c r="F25" s="3">
         <v>0.0</v>
       </c>
-      <c r="G25" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="3">
         <v>40.0</v>
       </c>
@@ -5836,9 +5790,7 @@
       <c r="F26" s="3">
         <v>0.0</v>
       </c>
-      <c r="G26" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G26" s="3"/>
       <c r="H26" s="3">
         <v>40.0</v>
       </c>
@@ -5875,9 +5827,7 @@
       <c r="F27" s="3">
         <v>0.0</v>
       </c>
-      <c r="G27" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G27" s="3"/>
       <c r="H27" s="3">
         <v>40.0</v>
       </c>
@@ -5914,9 +5864,7 @@
       <c r="F28" s="3">
         <v>0.0</v>
       </c>
-      <c r="G28" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G28" s="3"/>
       <c r="H28" s="3">
         <v>40.0</v>
       </c>
@@ -5953,9 +5901,7 @@
       <c r="F29" s="3">
         <v>0.0</v>
       </c>
-      <c r="G29" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G29" s="3"/>
       <c r="H29" s="3">
         <v>40.0</v>
       </c>
@@ -5992,9 +5938,7 @@
       <c r="F30" s="3">
         <v>0.0</v>
       </c>
-      <c r="G30" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G30" s="3"/>
       <c r="H30" s="3">
         <v>40.0</v>
       </c>
@@ -6031,9 +5975,7 @@
       <c r="F31" s="3">
         <v>0.0</v>
       </c>
-      <c r="G31" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G31" s="3"/>
       <c r="H31" s="3">
         <v>40.0</v>
       </c>
@@ -6070,9 +6012,7 @@
       <c r="F32" s="3">
         <v>0.0</v>
       </c>
-      <c r="G32" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G32" s="3"/>
       <c r="H32" s="3">
         <v>40.0</v>
       </c>
@@ -6109,9 +6049,7 @@
       <c r="F33" s="3">
         <v>0.0</v>
       </c>
-      <c r="G33" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G33" s="3"/>
       <c r="H33" s="3">
         <v>40.0</v>
       </c>
@@ -6148,9 +6086,7 @@
       <c r="F34" s="3">
         <v>0.0</v>
       </c>
-      <c r="G34" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G34" s="3"/>
       <c r="H34" s="3">
         <v>40.0</v>
       </c>
@@ -6187,9 +6123,7 @@
       <c r="F35" s="3">
         <v>0.0</v>
       </c>
-      <c r="G35" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G35" s="3"/>
       <c r="H35" s="3">
         <v>40.0</v>
       </c>
@@ -6226,9 +6160,7 @@
       <c r="F36" s="3">
         <v>0.0</v>
       </c>
-      <c r="G36" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G36" s="3"/>
       <c r="H36" s="3">
         <v>40.0</v>
       </c>
@@ -6265,9 +6197,7 @@
       <c r="F37" s="3">
         <v>0.0</v>
       </c>
-      <c r="G37" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G37" s="3"/>
       <c r="H37" s="3">
         <v>40.0</v>
       </c>
@@ -6304,9 +6234,7 @@
       <c r="F38" s="3">
         <v>0.0</v>
       </c>
-      <c r="G38" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G38" s="3"/>
       <c r="H38" s="3">
         <v>40.0</v>
       </c>
@@ -6343,9 +6271,7 @@
       <c r="F39" s="3">
         <v>0.0</v>
       </c>
-      <c r="G39" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G39" s="3"/>
       <c r="H39" s="3">
         <v>40.0</v>
       </c>
@@ -6382,9 +6308,7 @@
       <c r="F40" s="3">
         <v>0.0</v>
       </c>
-      <c r="G40" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G40" s="3"/>
       <c r="H40" s="3">
         <v>40.0</v>
       </c>
@@ -6421,9 +6345,7 @@
       <c r="F41" s="3">
         <v>0.0</v>
       </c>
-      <c r="G41" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G41" s="3"/>
       <c r="H41" s="3">
         <v>40.0</v>
       </c>
@@ -6460,9 +6382,7 @@
       <c r="F42" s="3">
         <v>0.0</v>
       </c>
-      <c r="G42" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G42" s="3"/>
       <c r="H42" s="3">
         <v>40.0</v>
       </c>
@@ -6499,9 +6419,7 @@
       <c r="F43" s="3">
         <v>0.0</v>
       </c>
-      <c r="G43" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G43" s="3"/>
       <c r="H43" s="3">
         <v>40.0</v>
       </c>
@@ -6538,9 +6456,7 @@
       <c r="F44" s="3">
         <v>0.0</v>
       </c>
-      <c r="G44" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="3">
         <v>40.0</v>
       </c>
@@ -6577,9 +6493,7 @@
       <c r="F45" s="3">
         <v>0.0</v>
       </c>
-      <c r="G45" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G45" s="3"/>
       <c r="H45" s="3">
         <v>40.0</v>
       </c>
@@ -6616,9 +6530,7 @@
       <c r="F46" s="3">
         <v>0.0</v>
       </c>
-      <c r="G46" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G46" s="3"/>
       <c r="H46" s="3">
         <v>40.0</v>
       </c>
@@ -6655,9 +6567,7 @@
       <c r="F47" s="3">
         <v>0.0</v>
       </c>
-      <c r="G47" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G47" s="3"/>
       <c r="H47" s="3">
         <v>40.0</v>
       </c>
@@ -6694,9 +6604,7 @@
       <c r="F48" s="3">
         <v>0.0</v>
       </c>
-      <c r="G48" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G48" s="3"/>
       <c r="H48" s="3">
         <v>40.0</v>
       </c>
@@ -6733,9 +6641,7 @@
       <c r="F49" s="3">
         <v>0.0</v>
       </c>
-      <c r="G49" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G49" s="3"/>
       <c r="H49" s="3">
         <v>40.0</v>
       </c>
@@ -6772,9 +6678,7 @@
       <c r="F50" s="3">
         <v>0.0</v>
       </c>
-      <c r="G50" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G50" s="3"/>
       <c r="H50" s="3">
         <v>40.0</v>
       </c>
@@ -6811,9 +6715,7 @@
       <c r="F51" s="3">
         <v>0.0</v>
       </c>
-      <c r="G51" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G51" s="3"/>
       <c r="H51" s="3">
         <v>40.0</v>
       </c>
@@ -6850,9 +6752,7 @@
       <c r="F52" s="3">
         <v>0.0</v>
       </c>
-      <c r="G52" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G52" s="3"/>
       <c r="H52" s="3">
         <v>40.0</v>
       </c>
@@ -6889,9 +6789,7 @@
       <c r="F53">
         <v>0.0</v>
       </c>
-      <c r="G53">
-        <v>100.0</v>
-      </c>
+      <c r="G53"/>
       <c r="H53">
         <v>40.0</v>
       </c>
@@ -6928,9 +6826,7 @@
       <c r="F54">
         <v>0.0</v>
       </c>
-      <c r="G54">
-        <v>100.0</v>
-      </c>
+      <c r="G54"/>
       <c r="H54">
         <v>40.0</v>
       </c>
@@ -6967,9 +6863,7 @@
       <c r="F55">
         <v>0.0</v>
       </c>
-      <c r="G55">
-        <v>100.0</v>
-      </c>
+      <c r="G55"/>
       <c r="H55">
         <v>40.0</v>
       </c>
@@ -7006,9 +6900,7 @@
       <c r="F56">
         <v>0.0</v>
       </c>
-      <c r="G56">
-        <v>100.0</v>
-      </c>
+      <c r="G56"/>
       <c r="H56">
         <v>40.0</v>
       </c>
@@ -7045,9 +6937,7 @@
       <c r="F57">
         <v>0.0</v>
       </c>
-      <c r="G57">
-        <v>100.0</v>
-      </c>
+      <c r="G57"/>
       <c r="H57">
         <v>40.0</v>
       </c>
@@ -7084,9 +6974,7 @@
       <c r="F58">
         <v>0.0</v>
       </c>
-      <c r="G58">
-        <v>100.0</v>
-      </c>
+      <c r="G58"/>
       <c r="H58">
         <v>40.0</v>
       </c>
@@ -7123,9 +7011,7 @@
       <c r="F59">
         <v>0.0</v>
       </c>
-      <c r="G59">
-        <v>100.0</v>
-      </c>
+      <c r="G59"/>
       <c r="H59">
         <v>40.0</v>
       </c>
@@ -7162,9 +7048,7 @@
       <c r="F60">
         <v>9.7971508809</v>
       </c>
-      <c r="G60">
-        <v>100.0</v>
-      </c>
+      <c r="G60"/>
       <c r="H60">
         <v>40.0</v>
       </c>
@@ -7201,9 +7085,7 @@
       <c r="F61">
         <v>27.2316188372</v>
       </c>
-      <c r="G61">
-        <v>100.0</v>
-      </c>
+      <c r="G61"/>
       <c r="H61">
         <v>40.0</v>
       </c>
@@ -7240,9 +7122,7 @@
       <c r="F62">
         <v>44.6660867934</v>
       </c>
-      <c r="G62">
-        <v>100.0</v>
-      </c>
+      <c r="G62"/>
       <c r="H62">
         <v>40.0</v>
       </c>
@@ -7279,9 +7159,7 @@
       <c r="F63">
         <v>62.1005547496</v>
       </c>
-      <c r="G63">
-        <v>100.0</v>
-      </c>
+      <c r="G63"/>
       <c r="H63">
         <v>40.0</v>
       </c>
@@ -7318,9 +7196,7 @@
       <c r="F64">
         <v>79.5350227058</v>
       </c>
-      <c r="G64">
-        <v>100.0</v>
-      </c>
+      <c r="G64"/>
       <c r="H64">
         <v>40.0</v>
       </c>
@@ -7357,9 +7233,7 @@
       <c r="F65">
         <v>96.969490662</v>
       </c>
-      <c r="G65">
-        <v>100.0</v>
-      </c>
+      <c r="G65"/>
       <c r="H65">
         <v>40.0</v>
       </c>
@@ -7396,9 +7270,7 @@
       <c r="F66">
         <v>114.4039586182</v>
       </c>
-      <c r="G66">
-        <v>100.0</v>
-      </c>
+      <c r="G66"/>
       <c r="H66">
         <v>40.0</v>
       </c>
@@ -7435,9 +7307,7 @@
       <c r="F67">
         <v>131.8384265744</v>
       </c>
-      <c r="G67">
-        <v>100.0</v>
-      </c>
+      <c r="G67"/>
       <c r="H67">
         <v>40.0</v>
       </c>
@@ -7474,9 +7344,7 @@
       <c r="F68">
         <v>40.0</v>
       </c>
-      <c r="G68">
-        <v>100.0</v>
-      </c>
+      <c r="G68"/>
       <c r="H68">
         <v>40.0</v>
       </c>
@@ -7513,9 +7381,7 @@
       <c r="F69">
         <v>80.0</v>
       </c>
-      <c r="G69">
-        <v>100.0</v>
-      </c>
+      <c r="G69"/>
       <c r="H69">
         <v>40.0</v>
       </c>
@@ -7552,9 +7418,7 @@
       <c r="F70">
         <v>120.0</v>
       </c>
-      <c r="G70">
-        <v>100.0</v>
-      </c>
+      <c r="G70"/>
       <c r="H70">
         <v>40.0</v>
       </c>
@@ -7591,9 +7455,7 @@
       <c r="F71">
         <v>160.0</v>
       </c>
-      <c r="G71">
-        <v>100.0</v>
-      </c>
+      <c r="G71"/>
       <c r="H71">
         <v>40.0</v>
       </c>
@@ -7630,9 +7492,7 @@
       <c r="F72">
         <v>200.0</v>
       </c>
-      <c r="G72">
-        <v>100.0</v>
-      </c>
+      <c r="G72"/>
       <c r="H72">
         <v>40.0</v>
       </c>
@@ -7669,9 +7529,7 @@
       <c r="F73">
         <v>240.0</v>
       </c>
-      <c r="G73">
-        <v>100.0</v>
-      </c>
+      <c r="G73"/>
       <c r="H73">
         <v>40.0</v>
       </c>
@@ -7708,9 +7566,7 @@
       <c r="F74">
         <v>280.0</v>
       </c>
-      <c r="G74">
-        <v>100.0</v>
-      </c>
+      <c r="G74"/>
       <c r="H74">
         <v>40.0</v>
       </c>
@@ -7747,9 +7603,7 @@
       <c r="F75">
         <v>320.0</v>
       </c>
-      <c r="G75">
-        <v>100.0</v>
-      </c>
+      <c r="G75"/>
       <c r="H75">
         <v>40.0</v>
       </c>
@@ -7786,9 +7640,7 @@
       <c r="F76">
         <v>360.0</v>
       </c>
-      <c r="G76">
-        <v>100.0</v>
-      </c>
+      <c r="G76"/>
       <c r="H76">
         <v>40.0</v>
       </c>
@@ -10469,14 +10321,14 @@
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>elastic</t>
+          <t>mc</t>
         </is>
       </c>
       <c r="F11" s="3">
-        <v>0.0</v>
+        <v>675.0</v>
       </c>
       <c r="G11" s="3">
-        <v>0.0</v>
+        <v>43.0</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3">

--- a/docs/verification/files/rocscience/joints/rj005.xlsx
+++ b/docs/verification/files/rocscience/joints/rj005.xlsx
@@ -4939,7 +4939,9 @@
       <c r="F3" s="3">
         <v>0.0</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H3" s="3">
         <v>40.0</v>
       </c>
@@ -4976,7 +4978,9 @@
       <c r="F4" s="3">
         <v>0.0</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H4" s="3">
         <v>40.0</v>
       </c>
@@ -5013,7 +5017,9 @@
       <c r="F5" s="3">
         <v>0.0</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H5" s="3">
         <v>40.0</v>
       </c>
@@ -5050,7 +5056,9 @@
       <c r="F6" s="3">
         <v>0.0</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H6" s="3">
         <v>40.0</v>
       </c>
@@ -5087,7 +5095,9 @@
       <c r="F7" s="3">
         <v>0.0</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H7" s="3">
         <v>40.0</v>
       </c>
@@ -5124,7 +5134,9 @@
       <c r="F8" s="3">
         <v>0.0</v>
       </c>
-      <c r="G8" s="3"/>
+      <c r="G8" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H8" s="3">
         <v>40.0</v>
       </c>
@@ -5161,7 +5173,9 @@
       <c r="F9" s="3">
         <v>0.0</v>
       </c>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H9" s="3">
         <v>40.0</v>
       </c>
@@ -5198,7 +5212,9 @@
       <c r="F10" s="3">
         <v>0.0</v>
       </c>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H10" s="3">
         <v>40.0</v>
       </c>
@@ -5235,7 +5251,9 @@
       <c r="F11" s="3">
         <v>0.0</v>
       </c>
-      <c r="G11" s="3"/>
+      <c r="G11" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H11" s="3">
         <v>40.0</v>
       </c>
@@ -5272,7 +5290,9 @@
       <c r="F12" s="3">
         <v>0.0</v>
       </c>
-      <c r="G12" s="3"/>
+      <c r="G12" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H12" s="3">
         <v>40.0</v>
       </c>
@@ -5309,7 +5329,9 @@
       <c r="F13" s="3">
         <v>0.0</v>
       </c>
-      <c r="G13" s="3"/>
+      <c r="G13" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H13" s="3">
         <v>40.0</v>
       </c>
@@ -5346,7 +5368,9 @@
       <c r="F14" s="3">
         <v>0.0</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="G14" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H14" s="3">
         <v>40.0</v>
       </c>
@@ -5383,7 +5407,9 @@
       <c r="F15" s="3">
         <v>0.0</v>
       </c>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H15" s="3">
         <v>40.0</v>
       </c>
@@ -5420,7 +5446,9 @@
       <c r="F16" s="3">
         <v>0.0</v>
       </c>
-      <c r="G16" s="3"/>
+      <c r="G16" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H16" s="3">
         <v>40.0</v>
       </c>
@@ -5457,7 +5485,9 @@
       <c r="F17" s="3">
         <v>0.0</v>
       </c>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H17" s="3">
         <v>40.0</v>
       </c>
@@ -5494,7 +5524,9 @@
       <c r="F18" s="3">
         <v>0.0</v>
       </c>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H18" s="3">
         <v>40.0</v>
       </c>
@@ -5531,7 +5563,9 @@
       <c r="F19" s="3">
         <v>0.0</v>
       </c>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H19" s="3">
         <v>40.0</v>
       </c>
@@ -5568,7 +5602,9 @@
       <c r="F20" s="3">
         <v>0.0</v>
       </c>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H20" s="3">
         <v>40.0</v>
       </c>
@@ -5605,7 +5641,9 @@
       <c r="F21" s="3">
         <v>0.0</v>
       </c>
-      <c r="G21" s="3"/>
+      <c r="G21" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H21" s="3">
         <v>40.0</v>
       </c>
@@ -5642,7 +5680,9 @@
       <c r="F22" s="3">
         <v>0.0</v>
       </c>
-      <c r="G22" s="3"/>
+      <c r="G22" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H22" s="3">
         <v>40.0</v>
       </c>
@@ -5679,7 +5719,9 @@
       <c r="F23" s="3">
         <v>0.0</v>
       </c>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H23" s="3">
         <v>40.0</v>
       </c>
@@ -5716,7 +5758,9 @@
       <c r="F24" s="3">
         <v>0.0</v>
       </c>
-      <c r="G24" s="3"/>
+      <c r="G24" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H24" s="3">
         <v>40.0</v>
       </c>
@@ -5753,7 +5797,9 @@
       <c r="F25" s="3">
         <v>0.0</v>
       </c>
-      <c r="G25" s="3"/>
+      <c r="G25" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H25" s="3">
         <v>40.0</v>
       </c>
@@ -5790,7 +5836,9 @@
       <c r="F26" s="3">
         <v>0.0</v>
       </c>
-      <c r="G26" s="3"/>
+      <c r="G26" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H26" s="3">
         <v>40.0</v>
       </c>
@@ -5827,7 +5875,9 @@
       <c r="F27" s="3">
         <v>0.0</v>
       </c>
-      <c r="G27" s="3"/>
+      <c r="G27" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H27" s="3">
         <v>40.0</v>
       </c>
@@ -5864,7 +5914,9 @@
       <c r="F28" s="3">
         <v>0.0</v>
       </c>
-      <c r="G28" s="3"/>
+      <c r="G28" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H28" s="3">
         <v>40.0</v>
       </c>
@@ -5901,7 +5953,9 @@
       <c r="F29" s="3">
         <v>0.0</v>
       </c>
-      <c r="G29" s="3"/>
+      <c r="G29" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H29" s="3">
         <v>40.0</v>
       </c>
@@ -5938,7 +5992,9 @@
       <c r="F30" s="3">
         <v>0.0</v>
       </c>
-      <c r="G30" s="3"/>
+      <c r="G30" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H30" s="3">
         <v>40.0</v>
       </c>
@@ -5975,7 +6031,9 @@
       <c r="F31" s="3">
         <v>0.0</v>
       </c>
-      <c r="G31" s="3"/>
+      <c r="G31" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H31" s="3">
         <v>40.0</v>
       </c>
@@ -6012,7 +6070,9 @@
       <c r="F32" s="3">
         <v>0.0</v>
       </c>
-      <c r="G32" s="3"/>
+      <c r="G32" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H32" s="3">
         <v>40.0</v>
       </c>
@@ -6049,7 +6109,9 @@
       <c r="F33" s="3">
         <v>0.0</v>
       </c>
-      <c r="G33" s="3"/>
+      <c r="G33" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H33" s="3">
         <v>40.0</v>
       </c>
@@ -6086,7 +6148,9 @@
       <c r="F34" s="3">
         <v>0.0</v>
       </c>
-      <c r="G34" s="3"/>
+      <c r="G34" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H34" s="3">
         <v>40.0</v>
       </c>
@@ -6123,7 +6187,9 @@
       <c r="F35" s="3">
         <v>0.0</v>
       </c>
-      <c r="G35" s="3"/>
+      <c r="G35" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H35" s="3">
         <v>40.0</v>
       </c>
@@ -6160,7 +6226,9 @@
       <c r="F36" s="3">
         <v>0.0</v>
       </c>
-      <c r="G36" s="3"/>
+      <c r="G36" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H36" s="3">
         <v>40.0</v>
       </c>
@@ -6197,7 +6265,9 @@
       <c r="F37" s="3">
         <v>0.0</v>
       </c>
-      <c r="G37" s="3"/>
+      <c r="G37" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H37" s="3">
         <v>40.0</v>
       </c>
@@ -6234,7 +6304,9 @@
       <c r="F38" s="3">
         <v>0.0</v>
       </c>
-      <c r="G38" s="3"/>
+      <c r="G38" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H38" s="3">
         <v>40.0</v>
       </c>
@@ -6271,7 +6343,9 @@
       <c r="F39" s="3">
         <v>0.0</v>
       </c>
-      <c r="G39" s="3"/>
+      <c r="G39" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H39" s="3">
         <v>40.0</v>
       </c>
@@ -6308,7 +6382,9 @@
       <c r="F40" s="3">
         <v>0.0</v>
       </c>
-      <c r="G40" s="3"/>
+      <c r="G40" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H40" s="3">
         <v>40.0</v>
       </c>
@@ -6345,7 +6421,9 @@
       <c r="F41" s="3">
         <v>0.0</v>
       </c>
-      <c r="G41" s="3"/>
+      <c r="G41" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H41" s="3">
         <v>40.0</v>
       </c>
@@ -6382,7 +6460,9 @@
       <c r="F42" s="3">
         <v>0.0</v>
       </c>
-      <c r="G42" s="3"/>
+      <c r="G42" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H42" s="3">
         <v>40.0</v>
       </c>
@@ -6419,7 +6499,9 @@
       <c r="F43" s="3">
         <v>0.0</v>
       </c>
-      <c r="G43" s="3"/>
+      <c r="G43" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H43" s="3">
         <v>40.0</v>
       </c>
@@ -6456,7 +6538,9 @@
       <c r="F44" s="3">
         <v>0.0</v>
       </c>
-      <c r="G44" s="3"/>
+      <c r="G44" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H44" s="3">
         <v>40.0</v>
       </c>
@@ -6493,7 +6577,9 @@
       <c r="F45" s="3">
         <v>0.0</v>
       </c>
-      <c r="G45" s="3"/>
+      <c r="G45" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H45" s="3">
         <v>40.0</v>
       </c>
@@ -6530,7 +6616,9 @@
       <c r="F46" s="3">
         <v>0.0</v>
       </c>
-      <c r="G46" s="3"/>
+      <c r="G46" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H46" s="3">
         <v>40.0</v>
       </c>
@@ -6567,7 +6655,9 @@
       <c r="F47" s="3">
         <v>0.0</v>
       </c>
-      <c r="G47" s="3"/>
+      <c r="G47" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H47" s="3">
         <v>40.0</v>
       </c>
@@ -6604,7 +6694,9 @@
       <c r="F48" s="3">
         <v>0.0</v>
       </c>
-      <c r="G48" s="3"/>
+      <c r="G48" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H48" s="3">
         <v>40.0</v>
       </c>
@@ -6641,7 +6733,9 @@
       <c r="F49" s="3">
         <v>0.0</v>
       </c>
-      <c r="G49" s="3"/>
+      <c r="G49" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H49" s="3">
         <v>40.0</v>
       </c>
@@ -6678,7 +6772,9 @@
       <c r="F50" s="3">
         <v>0.0</v>
       </c>
-      <c r="G50" s="3"/>
+      <c r="G50" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H50" s="3">
         <v>40.0</v>
       </c>
@@ -6715,7 +6811,9 @@
       <c r="F51" s="3">
         <v>0.0</v>
       </c>
-      <c r="G51" s="3"/>
+      <c r="G51" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H51" s="3">
         <v>40.0</v>
       </c>
@@ -6752,7 +6850,9 @@
       <c r="F52" s="3">
         <v>0.0</v>
       </c>
-      <c r="G52" s="3"/>
+      <c r="G52" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H52" s="3">
         <v>40.0</v>
       </c>
@@ -6789,7 +6889,9 @@
       <c r="F53">
         <v>0.0</v>
       </c>
-      <c r="G53"/>
+      <c r="G53">
+        <v>100.0</v>
+      </c>
       <c r="H53">
         <v>40.0</v>
       </c>
@@ -6826,7 +6928,9 @@
       <c r="F54">
         <v>0.0</v>
       </c>
-      <c r="G54"/>
+      <c r="G54">
+        <v>100.0</v>
+      </c>
       <c r="H54">
         <v>40.0</v>
       </c>
@@ -6863,7 +6967,9 @@
       <c r="F55">
         <v>0.0</v>
       </c>
-      <c r="G55"/>
+      <c r="G55">
+        <v>100.0</v>
+      </c>
       <c r="H55">
         <v>40.0</v>
       </c>
@@ -6900,7 +7006,9 @@
       <c r="F56">
         <v>0.0</v>
       </c>
-      <c r="G56"/>
+      <c r="G56">
+        <v>100.0</v>
+      </c>
       <c r="H56">
         <v>40.0</v>
       </c>
@@ -6937,7 +7045,9 @@
       <c r="F57">
         <v>0.0</v>
       </c>
-      <c r="G57"/>
+      <c r="G57">
+        <v>100.0</v>
+      </c>
       <c r="H57">
         <v>40.0</v>
       </c>
@@ -6974,7 +7084,9 @@
       <c r="F58">
         <v>0.0</v>
       </c>
-      <c r="G58"/>
+      <c r="G58">
+        <v>100.0</v>
+      </c>
       <c r="H58">
         <v>40.0</v>
       </c>
@@ -7011,7 +7123,9 @@
       <c r="F59">
         <v>0.0</v>
       </c>
-      <c r="G59"/>
+      <c r="G59">
+        <v>100.0</v>
+      </c>
       <c r="H59">
         <v>40.0</v>
       </c>
@@ -7048,7 +7162,9 @@
       <c r="F60">
         <v>9.7971508809</v>
       </c>
-      <c r="G60"/>
+      <c r="G60">
+        <v>100.0</v>
+      </c>
       <c r="H60">
         <v>40.0</v>
       </c>
@@ -7085,7 +7201,9 @@
       <c r="F61">
         <v>27.2316188372</v>
       </c>
-      <c r="G61"/>
+      <c r="G61">
+        <v>100.0</v>
+      </c>
       <c r="H61">
         <v>40.0</v>
       </c>
@@ -7122,7 +7240,9 @@
       <c r="F62">
         <v>44.6660867934</v>
       </c>
-      <c r="G62"/>
+      <c r="G62">
+        <v>100.0</v>
+      </c>
       <c r="H62">
         <v>40.0</v>
       </c>
@@ -7159,7 +7279,9 @@
       <c r="F63">
         <v>62.1005547496</v>
       </c>
-      <c r="G63"/>
+      <c r="G63">
+        <v>100.0</v>
+      </c>
       <c r="H63">
         <v>40.0</v>
       </c>
@@ -7196,7 +7318,9 @@
       <c r="F64">
         <v>79.5350227058</v>
       </c>
-      <c r="G64"/>
+      <c r="G64">
+        <v>100.0</v>
+      </c>
       <c r="H64">
         <v>40.0</v>
       </c>
@@ -7233,7 +7357,9 @@
       <c r="F65">
         <v>96.969490662</v>
       </c>
-      <c r="G65"/>
+      <c r="G65">
+        <v>100.0</v>
+      </c>
       <c r="H65">
         <v>40.0</v>
       </c>
@@ -7270,7 +7396,9 @@
       <c r="F66">
         <v>114.4039586182</v>
       </c>
-      <c r="G66"/>
+      <c r="G66">
+        <v>100.0</v>
+      </c>
       <c r="H66">
         <v>40.0</v>
       </c>
@@ -7307,7 +7435,9 @@
       <c r="F67">
         <v>131.8384265744</v>
       </c>
-      <c r="G67"/>
+      <c r="G67">
+        <v>100.0</v>
+      </c>
       <c r="H67">
         <v>40.0</v>
       </c>
@@ -7344,7 +7474,9 @@
       <c r="F68">
         <v>40.0</v>
       </c>
-      <c r="G68"/>
+      <c r="G68">
+        <v>100.0</v>
+      </c>
       <c r="H68">
         <v>40.0</v>
       </c>
@@ -7381,7 +7513,9 @@
       <c r="F69">
         <v>80.0</v>
       </c>
-      <c r="G69"/>
+      <c r="G69">
+        <v>100.0</v>
+      </c>
       <c r="H69">
         <v>40.0</v>
       </c>
@@ -7418,7 +7552,9 @@
       <c r="F70">
         <v>120.0</v>
       </c>
-      <c r="G70"/>
+      <c r="G70">
+        <v>100.0</v>
+      </c>
       <c r="H70">
         <v>40.0</v>
       </c>
@@ -7455,7 +7591,9 @@
       <c r="F71">
         <v>160.0</v>
       </c>
-      <c r="G71"/>
+      <c r="G71">
+        <v>100.0</v>
+      </c>
       <c r="H71">
         <v>40.0</v>
       </c>
@@ -7492,7 +7630,9 @@
       <c r="F72">
         <v>200.0</v>
       </c>
-      <c r="G72"/>
+      <c r="G72">
+        <v>100.0</v>
+      </c>
       <c r="H72">
         <v>40.0</v>
       </c>
@@ -7529,7 +7669,9 @@
       <c r="F73">
         <v>240.0</v>
       </c>
-      <c r="G73"/>
+      <c r="G73">
+        <v>100.0</v>
+      </c>
       <c r="H73">
         <v>40.0</v>
       </c>
@@ -7566,7 +7708,9 @@
       <c r="F74">
         <v>280.0</v>
       </c>
-      <c r="G74"/>
+      <c r="G74">
+        <v>100.0</v>
+      </c>
       <c r="H74">
         <v>40.0</v>
       </c>
@@ -7603,7 +7747,9 @@
       <c r="F75">
         <v>320.0</v>
       </c>
-      <c r="G75"/>
+      <c r="G75">
+        <v>100.0</v>
+      </c>
       <c r="H75">
         <v>40.0</v>
       </c>
@@ -7640,7 +7786,9 @@
       <c r="F76">
         <v>360.0</v>
       </c>
-      <c r="G76"/>
+      <c r="G76">
+        <v>100.0</v>
+      </c>
       <c r="H76">
         <v>40.0</v>
       </c>
@@ -10321,14 +10469,14 @@
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>mc</t>
+          <t>elastic</t>
         </is>
       </c>
       <c r="F11" s="3">
-        <v>675.0</v>
+        <v>0.0</v>
       </c>
       <c r="G11" s="3">
-        <v>43.0</v>
+        <v>0.0</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3">

--- a/docs/verification/files/rocscience/joints/rj005.xlsx
+++ b/docs/verification/files/rocscience/joints/rj005.xlsx
@@ -4939,9 +4939,7 @@
       <c r="F3" s="3">
         <v>0.0</v>
       </c>
-      <c r="G3" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3">
         <v>40.0</v>
       </c>
@@ -4978,9 +4976,7 @@
       <c r="F4" s="3">
         <v>0.0</v>
       </c>
-      <c r="G4" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3">
         <v>40.0</v>
       </c>
@@ -5017,9 +5013,7 @@
       <c r="F5" s="3">
         <v>0.0</v>
       </c>
-      <c r="G5" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G5" s="3"/>
       <c r="H5" s="3">
         <v>40.0</v>
       </c>
@@ -5056,9 +5050,7 @@
       <c r="F6" s="3">
         <v>0.0</v>
       </c>
-      <c r="G6" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="3">
         <v>40.0</v>
       </c>
@@ -5095,9 +5087,7 @@
       <c r="F7" s="3">
         <v>0.0</v>
       </c>
-      <c r="G7" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3">
         <v>40.0</v>
       </c>
@@ -5134,9 +5124,7 @@
       <c r="F8" s="3">
         <v>0.0</v>
       </c>
-      <c r="G8" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G8" s="3"/>
       <c r="H8" s="3">
         <v>40.0</v>
       </c>
@@ -5173,9 +5161,7 @@
       <c r="F9" s="3">
         <v>0.0</v>
       </c>
-      <c r="G9" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G9" s="3"/>
       <c r="H9" s="3">
         <v>40.0</v>
       </c>
@@ -5212,9 +5198,7 @@
       <c r="F10" s="3">
         <v>0.0</v>
       </c>
-      <c r="G10" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G10" s="3"/>
       <c r="H10" s="3">
         <v>40.0</v>
       </c>
@@ -5251,9 +5235,7 @@
       <c r="F11" s="3">
         <v>0.0</v>
       </c>
-      <c r="G11" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G11" s="3"/>
       <c r="H11" s="3">
         <v>40.0</v>
       </c>
@@ -5290,9 +5272,7 @@
       <c r="F12" s="3">
         <v>0.0</v>
       </c>
-      <c r="G12" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G12" s="3"/>
       <c r="H12" s="3">
         <v>40.0</v>
       </c>
@@ -5329,9 +5309,7 @@
       <c r="F13" s="3">
         <v>0.0</v>
       </c>
-      <c r="G13" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3">
         <v>40.0</v>
       </c>
@@ -5368,9 +5346,7 @@
       <c r="F14" s="3">
         <v>0.0</v>
       </c>
-      <c r="G14" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G14" s="3"/>
       <c r="H14" s="3">
         <v>40.0</v>
       </c>
@@ -5407,9 +5383,7 @@
       <c r="F15" s="3">
         <v>0.0</v>
       </c>
-      <c r="G15" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G15" s="3"/>
       <c r="H15" s="3">
         <v>40.0</v>
       </c>
@@ -5446,9 +5420,7 @@
       <c r="F16" s="3">
         <v>0.0</v>
       </c>
-      <c r="G16" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="3">
         <v>40.0</v>
       </c>
@@ -5485,9 +5457,7 @@
       <c r="F17" s="3">
         <v>0.0</v>
       </c>
-      <c r="G17" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="3">
         <v>40.0</v>
       </c>
@@ -5524,9 +5494,7 @@
       <c r="F18" s="3">
         <v>0.0</v>
       </c>
-      <c r="G18" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="3">
         <v>40.0</v>
       </c>
@@ -5563,9 +5531,7 @@
       <c r="F19" s="3">
         <v>0.0</v>
       </c>
-      <c r="G19" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G19" s="3"/>
       <c r="H19" s="3">
         <v>40.0</v>
       </c>
@@ -5602,9 +5568,7 @@
       <c r="F20" s="3">
         <v>0.0</v>
       </c>
-      <c r="G20" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="3">
         <v>40.0</v>
       </c>
@@ -5641,9 +5605,7 @@
       <c r="F21" s="3">
         <v>0.0</v>
       </c>
-      <c r="G21" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="3">
         <v>40.0</v>
       </c>
@@ -5680,9 +5642,7 @@
       <c r="F22" s="3">
         <v>0.0</v>
       </c>
-      <c r="G22" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G22" s="3"/>
       <c r="H22" s="3">
         <v>40.0</v>
       </c>
@@ -5719,9 +5679,7 @@
       <c r="F23" s="3">
         <v>0.0</v>
       </c>
-      <c r="G23" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="3">
         <v>40.0</v>
       </c>
@@ -5758,9 +5716,7 @@
       <c r="F24" s="3">
         <v>0.0</v>
       </c>
-      <c r="G24" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="3">
         <v>40.0</v>
       </c>
@@ -5797,9 +5753,7 @@
       <c r="F25" s="3">
         <v>0.0</v>
       </c>
-      <c r="G25" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="3">
         <v>40.0</v>
       </c>
@@ -5836,9 +5790,7 @@
       <c r="F26" s="3">
         <v>0.0</v>
       </c>
-      <c r="G26" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G26" s="3"/>
       <c r="H26" s="3">
         <v>40.0</v>
       </c>
@@ -5875,9 +5827,7 @@
       <c r="F27" s="3">
         <v>0.0</v>
       </c>
-      <c r="G27" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G27" s="3"/>
       <c r="H27" s="3">
         <v>40.0</v>
       </c>
@@ -5914,9 +5864,7 @@
       <c r="F28" s="3">
         <v>0.0</v>
       </c>
-      <c r="G28" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G28" s="3"/>
       <c r="H28" s="3">
         <v>40.0</v>
       </c>
@@ -5953,9 +5901,7 @@
       <c r="F29" s="3">
         <v>0.0</v>
       </c>
-      <c r="G29" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G29" s="3"/>
       <c r="H29" s="3">
         <v>40.0</v>
       </c>
@@ -5992,9 +5938,7 @@
       <c r="F30" s="3">
         <v>0.0</v>
       </c>
-      <c r="G30" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G30" s="3"/>
       <c r="H30" s="3">
         <v>40.0</v>
       </c>
@@ -6031,9 +5975,7 @@
       <c r="F31" s="3">
         <v>0.0</v>
       </c>
-      <c r="G31" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G31" s="3"/>
       <c r="H31" s="3">
         <v>40.0</v>
       </c>
@@ -6070,9 +6012,7 @@
       <c r="F32" s="3">
         <v>0.0</v>
       </c>
-      <c r="G32" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G32" s="3"/>
       <c r="H32" s="3">
         <v>40.0</v>
       </c>
@@ -6109,9 +6049,7 @@
       <c r="F33" s="3">
         <v>0.0</v>
       </c>
-      <c r="G33" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G33" s="3"/>
       <c r="H33" s="3">
         <v>40.0</v>
       </c>
@@ -6148,9 +6086,7 @@
       <c r="F34" s="3">
         <v>0.0</v>
       </c>
-      <c r="G34" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G34" s="3"/>
       <c r="H34" s="3">
         <v>40.0</v>
       </c>
@@ -6187,9 +6123,7 @@
       <c r="F35" s="3">
         <v>0.0</v>
       </c>
-      <c r="G35" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G35" s="3"/>
       <c r="H35" s="3">
         <v>40.0</v>
       </c>
@@ -6226,9 +6160,7 @@
       <c r="F36" s="3">
         <v>0.0</v>
       </c>
-      <c r="G36" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G36" s="3"/>
       <c r="H36" s="3">
         <v>40.0</v>
       </c>
@@ -6265,9 +6197,7 @@
       <c r="F37" s="3">
         <v>0.0</v>
       </c>
-      <c r="G37" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G37" s="3"/>
       <c r="H37" s="3">
         <v>40.0</v>
       </c>
@@ -6304,9 +6234,7 @@
       <c r="F38" s="3">
         <v>0.0</v>
       </c>
-      <c r="G38" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G38" s="3"/>
       <c r="H38" s="3">
         <v>40.0</v>
       </c>
@@ -6343,9 +6271,7 @@
       <c r="F39" s="3">
         <v>0.0</v>
       </c>
-      <c r="G39" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G39" s="3"/>
       <c r="H39" s="3">
         <v>40.0</v>
       </c>
@@ -6382,9 +6308,7 @@
       <c r="F40" s="3">
         <v>0.0</v>
       </c>
-      <c r="G40" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G40" s="3"/>
       <c r="H40" s="3">
         <v>40.0</v>
       </c>
@@ -6421,9 +6345,7 @@
       <c r="F41" s="3">
         <v>0.0</v>
       </c>
-      <c r="G41" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G41" s="3"/>
       <c r="H41" s="3">
         <v>40.0</v>
       </c>
@@ -6460,9 +6382,7 @@
       <c r="F42" s="3">
         <v>0.0</v>
       </c>
-      <c r="G42" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G42" s="3"/>
       <c r="H42" s="3">
         <v>40.0</v>
       </c>
@@ -6499,9 +6419,7 @@
       <c r="F43" s="3">
         <v>0.0</v>
       </c>
-      <c r="G43" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G43" s="3"/>
       <c r="H43" s="3">
         <v>40.0</v>
       </c>
@@ -6538,9 +6456,7 @@
       <c r="F44" s="3">
         <v>0.0</v>
       </c>
-      <c r="G44" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="3">
         <v>40.0</v>
       </c>
@@ -6577,9 +6493,7 @@
       <c r="F45" s="3">
         <v>0.0</v>
       </c>
-      <c r="G45" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G45" s="3"/>
       <c r="H45" s="3">
         <v>40.0</v>
       </c>
@@ -6616,9 +6530,7 @@
       <c r="F46" s="3">
         <v>0.0</v>
       </c>
-      <c r="G46" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G46" s="3"/>
       <c r="H46" s="3">
         <v>40.0</v>
       </c>
@@ -6655,9 +6567,7 @@
       <c r="F47" s="3">
         <v>0.0</v>
       </c>
-      <c r="G47" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G47" s="3"/>
       <c r="H47" s="3">
         <v>40.0</v>
       </c>
@@ -6694,9 +6604,7 @@
       <c r="F48" s="3">
         <v>0.0</v>
       </c>
-      <c r="G48" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G48" s="3"/>
       <c r="H48" s="3">
         <v>40.0</v>
       </c>
@@ -6733,9 +6641,7 @@
       <c r="F49" s="3">
         <v>0.0</v>
       </c>
-      <c r="G49" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G49" s="3"/>
       <c r="H49" s="3">
         <v>40.0</v>
       </c>
@@ -6772,9 +6678,7 @@
       <c r="F50" s="3">
         <v>0.0</v>
       </c>
-      <c r="G50" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G50" s="3"/>
       <c r="H50" s="3">
         <v>40.0</v>
       </c>
@@ -6811,9 +6715,7 @@
       <c r="F51" s="3">
         <v>0.0</v>
       </c>
-      <c r="G51" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G51" s="3"/>
       <c r="H51" s="3">
         <v>40.0</v>
       </c>
@@ -6850,9 +6752,7 @@
       <c r="F52" s="3">
         <v>0.0</v>
       </c>
-      <c r="G52" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G52" s="3"/>
       <c r="H52" s="3">
         <v>40.0</v>
       </c>
@@ -6889,9 +6789,7 @@
       <c r="F53">
         <v>0.0</v>
       </c>
-      <c r="G53">
-        <v>100.0</v>
-      </c>
+      <c r="G53"/>
       <c r="H53">
         <v>40.0</v>
       </c>
@@ -6928,9 +6826,7 @@
       <c r="F54">
         <v>0.0</v>
       </c>
-      <c r="G54">
-        <v>100.0</v>
-      </c>
+      <c r="G54"/>
       <c r="H54">
         <v>40.0</v>
       </c>
@@ -6967,9 +6863,7 @@
       <c r="F55">
         <v>0.0</v>
       </c>
-      <c r="G55">
-        <v>100.0</v>
-      </c>
+      <c r="G55"/>
       <c r="H55">
         <v>40.0</v>
       </c>
@@ -7006,9 +6900,7 @@
       <c r="F56">
         <v>0.0</v>
       </c>
-      <c r="G56">
-        <v>100.0</v>
-      </c>
+      <c r="G56"/>
       <c r="H56">
         <v>40.0</v>
       </c>
@@ -7045,9 +6937,7 @@
       <c r="F57">
         <v>0.0</v>
       </c>
-      <c r="G57">
-        <v>100.0</v>
-      </c>
+      <c r="G57"/>
       <c r="H57">
         <v>40.0</v>
       </c>
@@ -7084,9 +6974,7 @@
       <c r="F58">
         <v>0.0</v>
       </c>
-      <c r="G58">
-        <v>100.0</v>
-      </c>
+      <c r="G58"/>
       <c r="H58">
         <v>40.0</v>
       </c>
@@ -7123,9 +7011,7 @@
       <c r="F59">
         <v>0.0</v>
       </c>
-      <c r="G59">
-        <v>100.0</v>
-      </c>
+      <c r="G59"/>
       <c r="H59">
         <v>40.0</v>
       </c>
@@ -7162,9 +7048,7 @@
       <c r="F60">
         <v>9.7971508809</v>
       </c>
-      <c r="G60">
-        <v>100.0</v>
-      </c>
+      <c r="G60"/>
       <c r="H60">
         <v>40.0</v>
       </c>
@@ -7201,9 +7085,7 @@
       <c r="F61">
         <v>27.2316188372</v>
       </c>
-      <c r="G61">
-        <v>100.0</v>
-      </c>
+      <c r="G61"/>
       <c r="H61">
         <v>40.0</v>
       </c>
@@ -7240,9 +7122,7 @@
       <c r="F62">
         <v>44.6660867934</v>
       </c>
-      <c r="G62">
-        <v>100.0</v>
-      </c>
+      <c r="G62"/>
       <c r="H62">
         <v>40.0</v>
       </c>
@@ -7279,9 +7159,7 @@
       <c r="F63">
         <v>62.1005547496</v>
       </c>
-      <c r="G63">
-        <v>100.0</v>
-      </c>
+      <c r="G63"/>
       <c r="H63">
         <v>40.0</v>
       </c>
@@ -7318,9 +7196,7 @@
       <c r="F64">
         <v>79.5350227058</v>
       </c>
-      <c r="G64">
-        <v>100.0</v>
-      </c>
+      <c r="G64"/>
       <c r="H64">
         <v>40.0</v>
       </c>
@@ -7357,9 +7233,7 @@
       <c r="F65">
         <v>96.969490662</v>
       </c>
-      <c r="G65">
-        <v>100.0</v>
-      </c>
+      <c r="G65"/>
       <c r="H65">
         <v>40.0</v>
       </c>
@@ -7396,9 +7270,7 @@
       <c r="F66">
         <v>114.4039586182</v>
       </c>
-      <c r="G66">
-        <v>100.0</v>
-      </c>
+      <c r="G66"/>
       <c r="H66">
         <v>40.0</v>
       </c>
@@ -7435,9 +7307,7 @@
       <c r="F67">
         <v>131.8384265744</v>
       </c>
-      <c r="G67">
-        <v>100.0</v>
-      </c>
+      <c r="G67"/>
       <c r="H67">
         <v>40.0</v>
       </c>
@@ -7474,9 +7344,7 @@
       <c r="F68">
         <v>40.0</v>
       </c>
-      <c r="G68">
-        <v>100.0</v>
-      </c>
+      <c r="G68"/>
       <c r="H68">
         <v>40.0</v>
       </c>
@@ -7513,9 +7381,7 @@
       <c r="F69">
         <v>80.0</v>
       </c>
-      <c r="G69">
-        <v>100.0</v>
-      </c>
+      <c r="G69"/>
       <c r="H69">
         <v>40.0</v>
       </c>
@@ -7552,9 +7418,7 @@
       <c r="F70">
         <v>120.0</v>
       </c>
-      <c r="G70">
-        <v>100.0</v>
-      </c>
+      <c r="G70"/>
       <c r="H70">
         <v>40.0</v>
       </c>
@@ -7591,9 +7455,7 @@
       <c r="F71">
         <v>160.0</v>
       </c>
-      <c r="G71">
-        <v>100.0</v>
-      </c>
+      <c r="G71"/>
       <c r="H71">
         <v>40.0</v>
       </c>
@@ -7630,9 +7492,7 @@
       <c r="F72">
         <v>200.0</v>
       </c>
-      <c r="G72">
-        <v>100.0</v>
-      </c>
+      <c r="G72"/>
       <c r="H72">
         <v>40.0</v>
       </c>
@@ -7669,9 +7529,7 @@
       <c r="F73">
         <v>240.0</v>
       </c>
-      <c r="G73">
-        <v>100.0</v>
-      </c>
+      <c r="G73"/>
       <c r="H73">
         <v>40.0</v>
       </c>
@@ -7708,9 +7566,7 @@
       <c r="F74">
         <v>280.0</v>
       </c>
-      <c r="G74">
-        <v>100.0</v>
-      </c>
+      <c r="G74"/>
       <c r="H74">
         <v>40.0</v>
       </c>
@@ -7747,9 +7603,7 @@
       <c r="F75">
         <v>320.0</v>
       </c>
-      <c r="G75">
-        <v>100.0</v>
-      </c>
+      <c r="G75"/>
       <c r="H75">
         <v>40.0</v>
       </c>
@@ -7786,9 +7640,7 @@
       <c r="F76">
         <v>360.0</v>
       </c>
-      <c r="G76">
-        <v>100.0</v>
-      </c>
+      <c r="G76"/>
       <c r="H76">
         <v>40.0</v>
       </c>
